--- a/public/templates/자기소개서 양식.xlsx
+++ b/public/templates/자기소개서 양식.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="지원자 관리(서술형)" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="작성 안내" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet name="지원자 관리(서술형)" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="작성 안내" sheetId="2" state="visible" r:id="rId2"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -611,7 +611,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B12"/>
+  <dimension ref="A1:B13"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="18" customWidth="1" min="1" max="1"/>
@@ -625,124 +625,134 @@
         </is>
       </c>
     </row>
-    <row r="2">
-      <c r="A2" t="inlineStr"/>
-    </row>
+    <row r="2"/>
     <row r="3">
       <c r="A3" s="4" t="inlineStr">
         <is>
-          <t>모양</t>
+          <t>쓰는 곳</t>
         </is>
       </c>
       <c r="B3" s="5" t="inlineStr">
         <is>
-          <t>채용 사이트(마이다스인)에서 내려받은 자기소개서 파일과 같은 모양입니다. 사이트에서 받은 파일은 고치지 않고 그대로 올리면 됩니다.</t>
+          <t>사전스크리닝 검토 &gt; 새 검토 시작의 자기소개서 파일. 자기소개서 문항 답변에서 블라인드 위배를 찾는 데 씁니다.</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="4" t="inlineStr">
         <is>
-          <t>1행</t>
+          <t>모양</t>
         </is>
       </c>
       <c r="B4" s="5" t="inlineStr">
         <is>
-          <t>제목 줄입니다. 내용은 읽지 않습니다.</t>
+          <t>채용 사이트(마이다스인)에서 내려받은 자기소개서 파일과 같은 모양입니다. 사이트에서 받은 파일은 고치지 않고 그대로 올리면 됩니다.</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="4" t="inlineStr">
         <is>
-          <t>2행</t>
+          <t>1행</t>
         </is>
       </c>
       <c r="B5" s="5" t="inlineStr">
         <is>
-          <t>머리글 줄입니다. 머리글 이름으로 열을 찾으므로 열 순서는 바뀌어도 됩니다.</t>
+          <t>제목 줄입니다. 내용은 읽지 않습니다.</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="4" t="inlineStr">
         <is>
-          <t>3행부터</t>
+          <t>2행</t>
         </is>
       </c>
       <c r="B6" s="5" t="inlineStr">
         <is>
-          <t>지원자 한 명이 한 줄입니다. 3행의 예시 줄은 지우고 쓰세요.</t>
+          <t>머리글 줄입니다. 머리글 이름으로 열을 찾으므로 열 순서는 바뀌어도 됩니다.</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="4" t="inlineStr">
         <is>
-          <t>꼭 있어야 하는 열</t>
+          <t>3행부터</t>
         </is>
       </c>
       <c r="B7" s="5" t="inlineStr">
         <is>
-          <t>수험번호(또는 순번) 열 하나, 자기소개서 문항 열 하나 이상</t>
+          <t>지원자 한 명이 한 줄입니다. 3행의 예시 줄은 지우고 쓰세요.</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="4" t="inlineStr">
         <is>
-          <t>없어도 되는 열</t>
+          <t>꼭 있어야 하는 열</t>
         </is>
       </c>
       <c r="B8" s="5" t="inlineStr">
         <is>
-          <t>이름, 공고명, 채용구분명, 지원분야, 작성일자, 제출 여부 열</t>
+          <t>수험번호(또는 순번) 열 하나, 자기소개서 문항 열 하나 이상</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="4" t="inlineStr">
         <is>
-          <t>문항 열 머리글</t>
+          <t>없어도 되는 열</t>
         </is>
       </c>
       <c r="B9" s="5" t="inlineStr">
         <is>
-          <t>'자기소개서 : 1. 문항 내용' 또는 '자기소개서_1 : 문항 내용' 모양이면 됩니다. 문항 수는 공고마다 달라도 됩니다.</t>
+          <t>이름, 공고명, 채용구분명, 지원분야, 작성일자, 제출 여부 열</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="4" t="inlineStr">
         <is>
-          <t>공고명</t>
+          <t>문항 열 머리글</t>
         </is>
       </c>
       <c r="B10" s="5" t="inlineStr">
         <is>
-          <t>공고명 열이 있으면 검토 결과의 공고명으로 씁니다. 없으면 저장명, 그것도 없으면 파일 이름을 씁니다.</t>
+          <t>'자기소개서 : 1. 문항 내용' 또는 '자기소개서_1 : 문항 내용' 모양이면 됩니다. 문항 수는 공고마다 달라도 됩니다.</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="4" t="inlineStr">
         <is>
-          <t>시트</t>
+          <t>공고명</t>
         </is>
       </c>
       <c r="B11" s="5" t="inlineStr">
         <is>
-          <t>시트 이름은 상관없습니다. 이 안내 시트는 지우지 않아도 읽지 않습니다.</t>
+          <t>공고명 열이 있으면 검토 결과의 공고명으로 씁니다. 없으면 저장명, 그것도 없으면 파일 이름을 씁니다.</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="4" t="inlineStr">
         <is>
+          <t>시트</t>
+        </is>
+      </c>
+      <c r="B12" s="5" t="inlineStr">
+        <is>
+          <t>시트 이름은 상관없습니다. 이 안내 시트는 지우지 않아도 읽지 않습니다.</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="4" t="inlineStr">
+        <is>
           <t>암호</t>
         </is>
       </c>
-      <c r="B12" s="5" t="inlineStr">
+      <c r="B13" s="5" t="inlineStr">
         <is>
           <t>암호를 건 엑셀은 올릴 수 없습니다.</t>
         </is>

--- a/public/templates/자기소개서 양식.xlsx
+++ b/public/templates/자기소개서 양식.xlsx
@@ -611,7 +611,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B13"/>
+  <dimension ref="A1:B15"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="18" customWidth="1" min="1" max="1"/>
@@ -634,7 +634,7 @@
       </c>
       <c r="B3" s="5" t="inlineStr">
         <is>
-          <t>사전스크리닝 검토 &gt; 새 검토 시작의 자기소개서 파일. 자기소개서 문항 답변에서 블라인드 위배를 찾는 데 씁니다.</t>
+          <t>사전스크리닝 검토 &gt; 신규 검토 생성의 자기소개서 파일. 자기소개서 문항 답변에서 블라인드 위배를 찾는 데 씁니다.</t>
         </is>
       </c>
     </row>
@@ -682,7 +682,7 @@
       </c>
       <c r="B7" s="5" t="inlineStr">
         <is>
-          <t>지원자 한 명이 한 줄입니다. 3행의 예시 줄은 지우고 쓰세요.</t>
+          <t>지원자 한 명이 한 줄입니다. 3행의 예시 줄은 지우고 쓰세요. 지우지 않으면 예시 지원자와 예시 공고명이 검토에 들어갑니다. 문항 답변이 모두 비어 있거나 '-' 인 줄은 읽지 않습니다.</t>
         </is>
       </c>
     </row>
@@ -694,65 +694,89 @@
       </c>
       <c r="B8" s="5" t="inlineStr">
         <is>
-          <t>수험번호(또는 순번) 열 하나, 자기소개서 문항 열 하나 이상</t>
+          <t>수험번호(또는 순번) 열 하나, 자기소개서 문항 열 하나 이상. 두 열은 같은 머리글 줄에 있어야 합니다.</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="4" t="inlineStr">
         <is>
-          <t>없어도 되는 열</t>
+          <t>연결</t>
         </is>
       </c>
       <c r="B9" s="5" t="inlineStr">
         <is>
-          <t>이름, 공고명, 채용구분명, 지원분야, 작성일자, 제출 여부 열</t>
+          <t>지원정보 파일, 첨부 실적 폴더와 수험번호로 이어 붙입니다. 세 파일의 수험번호가 같아야 같은 지원자로 봅니다. 자기소개서를 올리면 지원정보 파일에서는 자기소개서에 있는 수험번호만 검토합니다.</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="4" t="inlineStr">
         <is>
-          <t>문항 열 머리글</t>
+          <t>없어도 되는 열</t>
         </is>
       </c>
       <c r="B10" s="5" t="inlineStr">
         <is>
-          <t>'자기소개서 : 1. 문항 내용' 또는 '자기소개서_1 : 문항 내용' 모양이면 됩니다. 문항 수는 공고마다 달라도 됩니다.</t>
+          <t>이름, 공고명, 채용구분명, 지원분야, 작성일자, 제출 여부 열</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="4" t="inlineStr">
         <is>
-          <t>공고명</t>
+          <t>문항 열 머리글</t>
         </is>
       </c>
       <c r="B11" s="5" t="inlineStr">
         <is>
-          <t>공고명 열이 있으면 검토 결과의 공고명으로 씁니다. 없으면 저장명, 그것도 없으면 파일 이름을 씁니다.</t>
+          <t>'자기소개서 : 1. 문항 내용' 또는 '자기소개서_1 : 문항 내용' 모양이면 됩니다. 문항 수는 공고마다 달라도 됩니다.</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="4" t="inlineStr">
         <is>
-          <t>시트</t>
+          <t>공고명</t>
         </is>
       </c>
       <c r="B12" s="5" t="inlineStr">
         <is>
-          <t>시트 이름은 상관없습니다. 이 안내 시트는 지우지 않아도 읽지 않습니다.</t>
+          <t>공고명 열이 있으면 검토 결과의 공고명으로 씁니다. 없으면 저장명, 그것도 없으면 파일 이름을 씁니다.</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="4" t="inlineStr">
         <is>
+          <t>시트</t>
+        </is>
+      </c>
+      <c r="B13" s="5" t="inlineStr">
+        <is>
+          <t>시트 이름은 상관없습니다. 자기소개서 시트가 여러 개면 모두 읽어 합칩니다. 이 안내 시트는 지우지 않아도 읽지 않습니다.</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="4" t="inlineStr">
+        <is>
+          <t>파일 형식</t>
+        </is>
+      </c>
+      <c r="B14" s="5" t="inlineStr">
+        <is>
+          <t>xlsx 만 올릴 수 있습니다.</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="4" t="inlineStr">
+        <is>
           <t>암호</t>
         </is>
       </c>
-      <c r="B13" s="5" t="inlineStr">
+      <c r="B15" s="5" t="inlineStr">
         <is>
           <t>암호를 건 엑셀은 올릴 수 없습니다.</t>
         </is>
